--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18712,7 +18730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18756,6 +18774,81 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1984_85_0321 'Lázně Bělohrad' ROZBITÝ prev CLUB_S1983_84_0280 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1984_85_0478 'TJ ND-ZŤS Sabinov' prev→CLUB_S1983_84_0467 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0010</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1984_85_0010 'Kvalifikace o 2. ČNHL – skupina A' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0011</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1984_85_0011 'Kvalifikace o 2. ČNHL – skupina B' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0012</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1984_85_0012 'Kvalifikace o 2. ČNHL – skupina C' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43981,6 @@
         </is>
       </c>
     </row>
-    <row r="450"/>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
@@ -44687,7 +44779,6 @@
         </is>
       </c>
     </row>
-    <row r="470"/>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
@@ -47158,6 +47249,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0321</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0321 'Lázně Bělohrad' ROZBITÝ prev CLUB_S1983_84_0280 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0478</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0478 'TJ ND-ZŤS Sabinov' prev→CLUB_S1983_84_0467 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0010</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1984_85_0010 'Kvalifikace o 2. ČNHL – skupina A' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0011</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1984_85_0011 'Kvalifikace o 2. ČNHL – skupina B' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0012</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1984_85_0012 'Kvalifikace o 2. ČNHL – skupina C' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4558,11 +4558,7 @@
           <t>CLUB_S1984_85_0321</t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0280</t>
-        </is>
-      </c>
+      <c r="R43" s="3" t="n"/>
       <c r="S43" s="3" t="n"/>
       <c r="T43" s="3" t="n"/>
       <c r="U43" s="3" t="n"/>
@@ -18730,7 +18726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18780,7 +18776,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1984_85_0321 'Lázně Bělohrad' ROZBITÝ prev CLUB_S1983_84_0280 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18792,7 +18788,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1984_85_0478 'TJ ND-ZŤS Sabinov' prev→CLUB_S1983_84_0467 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18802,14 +18798,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1984_85_0010</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1984_85_0010 'Kvalifikace o 2. ČNHL – skupina A' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18819,14 +18810,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1984_85_0011</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1984_85_0011 'Kvalifikace o 2. ČNHL – skupina B' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18836,17 +18822,468 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1984_85_0012</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1984_85_0012 'Kvalifikace o 2. ČNHL – skupina C' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaplice' → 'JZD Dubné' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24466,12 +24903,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25096,12 +25533,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -25180,12 +25617,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -25222,12 +25659,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -25437,12 +25874,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -25731,12 +26168,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -26482,12 +26919,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -26823,12 +27260,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -26954,12 +27391,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -27080,12 +27517,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -27206,12 +27643,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -27421,12 +27858,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -30212,12 +30649,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30375,12 +30812,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -30971,12 +31408,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -33029,12 +33466,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Oprava city: „RH Kaplice" → „Kaplice" (RH = Rudá hvězda, vojenský klub). || Kaplice = Jiskra/Slavoj Kaplice (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceský Krumlov). city Kaplice.</t>
+          <t>Oprava city: „RH Kaplice" → „Kaplice" (RH = Rudá hvězda, vojenský klub). || Kaplice = Jiskra/Slavoj Kaplice (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceský Krumlov). city Kaplice. || TBD: city 'Kaplice' → 'JZD Dubné' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Kaplice</t>
+          <t>JZD Dubné</t>
         </is>
       </c>
     </row>
@@ -33417,12 +33854,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -35154,12 +35591,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -35238,12 +35675,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -35280,12 +35717,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice.</t>
+          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice. || TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Třebenice</t>
+          <t>MDPM Lovosice</t>
         </is>
       </c>
     </row>
@@ -35401,12 +35838,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -35668,12 +36105,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov.</t>
+          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov. || TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Důl Jana Žižky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -35715,12 +36152,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -35851,12 +36288,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Železný Brod = TJ ŽB Železný Brod (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Jablonec nL Nisou). **Železný Brod** = sklarsky mesto (vyrobce sklenenych ozdob - bizuteria, perlicky). 'ŽB' = zkratka Železný Brod. city Železný Brod.</t>
+          <t>Železný Brod = TJ ŽB Železný Brod (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Jablonec nL Nisou). **Železný Brod** = sklarsky mesto (vyrobce sklenenych ozdob - bizuteria, perlicky). 'ŽB' = zkratka Železný Brod. city Železný Brod. || TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>ŽB Železný Brod</t>
+          <t>Železný Brod</t>
         </is>
       </c>
     </row>
@@ -36481,12 +36918,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -36565,12 +37002,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -37653,14 +38090,9 @@
           <t>okres Jičín:</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0280</t>
-        </is>
-      </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Spartak Lázně Bělohrad. city ✓. || Lázně Bělohrad = Spartak Lázně Bělohrad (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Lázně Bělohrad.</t>
+          <t>Spartak Lázně Bělohrad. city ✓. || Lázně Bělohrad = Spartak Lázně Bělohrad (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Lázně Bělohrad. || TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -39700,12 +40132,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -40083,12 +40515,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -40461,12 +40893,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -40906,12 +41338,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška.</t>
+          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška. || TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>RICO Veverská Bítýška</t>
+          <t>Veverská Bítýška</t>
         </is>
       </c>
     </row>
@@ -42862,12 +43294,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -43003,12 +43435,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -43972,15 +44404,16 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
-        </is>
-      </c>
-    </row>
+          <t>Nové Zámky</t>
+        </is>
+      </c>
+    </row>
+    <row r="450"/>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
@@ -44486,12 +44919,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -44779,6 +45212,7 @@
         </is>
       </c>
     </row>
+    <row r="470"/>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
@@ -47255,11 +47689,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -47304,21 +47738,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0321</t>
+          <t>CLUB_S1984_85_0005</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0321 'Lázně Bělohrad' ROZBITÝ prev CLUB_S1983_84_0280 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -47326,21 +47758,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0478</t>
+          <t>CLUB_S1984_85_0020</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0478 'TJ ND-ZŤS Sabinov' prev→CLUB_S1983_84_0467 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -47348,21 +47778,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1984_85_0010</t>
+          <t>CLUB_S1984_85_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1984_85_0010 'Kvalifikace o 2. ČNHL – skupina A' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -47370,21 +47798,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1984_85_0011</t>
+          <t>CLUB_S1984_85_0023</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1984_85_0011 'Kvalifikace o 2. ČNHL – skupina B' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -47392,24 +47818,782 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1984_85_0012</t>
+          <t>CLUB_S1984_85_0029</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1984_85_0012 'Kvalifikace o 2. ČNHL – skupina C' (L35, parent=NODE_S1984_85_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0036</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0063</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0071</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0074</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0077</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0080</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0085</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0149</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0153</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0153</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0166</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0210</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaplice' → 'JZD Dubné' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0219</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0262</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0264</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0265</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0267</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0268</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0274</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0275</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0278</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0291</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0294</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0296</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0309</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0321</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0367</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0372</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0376</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0384</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0385</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0395</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0397</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0440</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0443</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0466</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0478</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1984_85_0479</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65500,6 +66684,11 @@
           <t>CLUB_S1983_84_0244</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>TR_S1984_85_00182</t>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18726,7 +18726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18776,7 +18776,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18788,7 +18788,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18800,7 +18800,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18812,7 +18812,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18824,7 +18824,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18836,7 +18836,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18860,7 +18860,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18872,7 +18872,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18884,7 +18884,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18896,7 +18896,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18908,7 +18908,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18920,7 +18920,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18944,7 +18944,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18956,7 +18956,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -18968,7 +18968,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaplice' → 'JZD Dubné' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18980,7 +18980,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18992,7 +18992,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19004,7 +19004,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19028,7 +19028,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19040,7 +19040,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19052,7 +19052,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19064,7 +19064,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19076,7 +19076,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19088,7 +19088,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19112,7 +19112,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19124,7 +19124,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19136,7 +19136,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19148,7 +19148,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -19160,130 +19160,10 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19300,7 +19180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19359,6 +19239,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19401,6 +19286,11 @@
           <t>12 týmů + kvalifikace o ligu (tabulka). Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19448,6 +19338,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19537,6 +19432,11 @@
           <t>ASD Dukla Jihlava "B" hrála svá domácí utkání v Písku.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19579,6 +19479,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19972,6 +19877,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20098,6 +20008,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20224,6 +20139,11 @@
           <t>II.ČNHL: 3 skupiny. Kval o I.ČNHL.</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20266,6 +20186,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20308,6 +20233,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -20355,6 +20285,11 @@
           <t>Finále II. ČNHL. ASD Dukla Jihlava "B" hrála domácí utkání v Písku.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20439,6 +20374,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20481,6 +20421,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20523,6 +20468,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20565,6 +20515,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20607,6 +20562,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20691,6 +20651,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0030</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -20822,6 +20787,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0035</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -21074,6 +21044,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0040</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21116,6 +21091,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21252,6 +21232,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21294,6 +21279,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -21336,6 +21326,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -21378,6 +21373,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -21420,6 +21420,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -21546,6 +21551,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0050</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -21593,6 +21603,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0051</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -21635,6 +21650,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0052</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -21677,6 +21697,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0053</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -21719,6 +21744,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0054</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21761,6 +21791,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0055</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -21803,6 +21838,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0056</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -21845,6 +21885,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0057</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -21887,6 +21932,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0058</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21929,6 +21979,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0059</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22144,6 +22199,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0075</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22186,6 +22246,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0076</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22228,6 +22293,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0077</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -22270,6 +22340,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0078</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22443,6 +22518,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0082</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22485,6 +22565,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0077</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22527,6 +22612,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0078</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -22569,6 +22659,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0086</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -22611,6 +22706,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0087</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -22693,6 +22793,11 @@
       <c r="J79" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0090</t>
         </is>
       </c>
     </row>
@@ -24903,12 +25008,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25533,12 +25638,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -25659,12 +25764,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -26168,12 +26273,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -30812,12 +30917,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -33466,12 +33571,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Oprava city: „RH Kaplice" → „Kaplice" (RH = Rudá hvězda, vojenský klub). || Kaplice = Jiskra/Slavoj Kaplice (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceský Krumlov). city Kaplice. || TBD: city 'Kaplice' → 'JZD Dubné' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „RH Kaplice" → „Kaplice" (RH = Rudá hvězda, vojenský klub). || Kaplice = Jiskra/Slavoj Kaplice (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceský Krumlov). city Kaplice.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>JZD Dubné</t>
+          <t>Kaplice</t>
         </is>
       </c>
     </row>
@@ -35717,12 +35822,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice. || TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>MDPM Lovosice</t>
+          <t>Třebenice</t>
         </is>
       </c>
     </row>
@@ -37002,12 +37107,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -40132,12 +40237,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -43435,12 +43540,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -47689,7 +47794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -47743,12 +47848,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0005</t>
+          <t>CLUB_S1984_85_0022</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47763,12 +47868,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0020</t>
+          <t>CLUB_S1984_85_0029</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47783,12 +47888,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0022</t>
+          <t>CLUB_S1984_85_0063</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47803,12 +47908,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0023</t>
+          <t>CLUB_S1984_85_0071</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47823,12 +47928,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0029</t>
+          <t>CLUB_S1984_85_0074</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47843,12 +47948,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0036</t>
+          <t>CLUB_S1984_85_0077</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47863,12 +47968,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0063</t>
+          <t>CLUB_S1984_85_0080</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47883,12 +47988,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0071</t>
+          <t>CLUB_S1984_85_0085</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47903,12 +48008,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0074</t>
+          <t>CLUB_S1984_85_0149</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47923,12 +48028,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0077</t>
+          <t>CLUB_S1984_85_0153</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47943,12 +48048,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0080</t>
+          <t>CLUB_S1984_85_0166</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47963,12 +48068,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0085</t>
+          <t>CLUB_S1984_85_0219</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47983,12 +48088,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0149</t>
+          <t>CLUB_S1984_85_0262</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48003,12 +48108,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0153</t>
+          <t>CLUB_S1984_85_0264</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48023,12 +48128,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0153</t>
+          <t>CLUB_S1984_85_0267</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -48043,12 +48148,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0166</t>
+          <t>CLUB_S1984_85_0268</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48063,12 +48168,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0210</t>
+          <t>CLUB_S1984_85_0274</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaplice' → 'JZD Dubné' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48083,12 +48188,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0219</t>
+          <t>CLUB_S1984_85_0275</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48103,12 +48208,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0262</t>
+          <t>CLUB_S1984_85_0278</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48123,12 +48228,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0264</t>
+          <t>CLUB_S1984_85_0291</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -48143,12 +48248,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0265</t>
+          <t>CLUB_S1984_85_0294</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48163,12 +48268,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0267</t>
+          <t>CLUB_S1984_85_0309</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48183,12 +48288,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0268</t>
+          <t>CLUB_S1984_85_0321</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -48203,12 +48308,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0274</t>
+          <t>CLUB_S1984_85_0372</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -48223,12 +48328,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0275</t>
+          <t>CLUB_S1984_85_0376</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48243,12 +48348,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0278</t>
+          <t>CLUB_S1984_85_0384</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48263,12 +48368,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0291</t>
+          <t>CLUB_S1984_85_0385</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48283,12 +48388,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0294</t>
+          <t>CLUB_S1984_85_0395</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48303,12 +48408,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0296</t>
+          <t>CLUB_S1984_85_0397</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -48323,12 +48428,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0309</t>
+          <t>CLUB_S1984_85_0440</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48343,12 +48448,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0321</t>
+          <t>CLUB_S1984_85_0466</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48363,12 +48468,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0367</t>
+          <t>CLUB_S1984_85_0478</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48383,217 +48488,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0372</t>
+          <t>CLUB_S1984_85_0479</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0376</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0384</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0385</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0395</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0397</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0440</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0443</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0466</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0478</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0479</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / TJ Družstevník Rakovec nad Ondavou — odstoupil v průběhu soutěže</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
@@ -18726,7 +18726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18774,33 +18774,43 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] odstoupila družstva Horymír Neumětely a Jiskra Dolní Bousov</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30VYSL</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] TJ Družstevník Rakovec nad Ondavou — odstoupil v průběhu soutěže (club_id: CLUB_S1984_85_0477)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18812,7 +18822,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18824,7 +18834,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18836,7 +18846,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18848,7 +18858,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18860,7 +18870,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18872,7 +18882,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18884,7 +18894,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18896,7 +18906,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18908,7 +18918,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18920,7 +18930,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18932,7 +18942,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18944,7 +18954,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18956,7 +18966,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -18968,7 +18978,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18980,7 +18990,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18992,7 +19002,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19004,7 +19014,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19016,7 +19026,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19028,7 +19038,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19040,7 +19050,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19052,7 +19062,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19064,7 +19074,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19076,7 +19086,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19100,7 +19110,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19112,7 +19122,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19124,7 +19134,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19136,7 +19146,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19148,7 +19158,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -19160,10 +19170,46 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'TJ Družstevník Rakovec nad Ondavou — odstoupil v průběhu soutěže' [fix_club_notes_in_block_name]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -44935,7 +44981,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>Rakovec nad Ondavou = TJ Družstevník Rakovec nad Ondavou (Wiki D42 - registr ustavy 04/2026). Slovensky/Košický kraj (okres Michalovce). city Rakovec nad Ondavou.</t>
+          <t>Rakovec nad Ondavou = TJ Družstevník Rakovec nad Ondavou (Wiki D42 - registr ustavy 04/2026). Slovensky/Košický kraj (okres Michalovce). city Rakovec nad Ondavou. || TBD: extrahováno z block_name: 'TJ Družstevník Rakovec nad Ondavou — odstoupil v průběhu soutěže' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -47794,7 +47840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48468,12 +48514,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1984_85_0478</t>
+          <t>CLUB_S1984_85_0477</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: extrahováno z block_name: 'TJ Družstevník Rakovec nad Ondavou — odstoupil v průběhu soutěže' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -48488,17 +48534,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>CLUB_S1984_85_0478</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>CLUB_S1984_85_0479</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F34"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -55896,7 +55962,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / skupina D / odstoupila družstva Horymír Neumětely a Jiskra Dolní Bousov</t>
+          <t>Krajský přebor / skupina D</t>
         </is>
       </c>
       <c r="C29" s="2" t="n"/>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -44564,7 +44564,6 @@
         </is>
       </c>
     </row>
-    <row r="450"/>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
@@ -45363,7 +45362,6 @@
         </is>
       </c>
     </row>
-    <row r="470"/>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -19226,7 +19226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19288,6 +19288,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -19572,6 +19572,16 @@
           <t>NODE_S1984_85_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19581,6 +19591,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -19614,6 +19632,8 @@
           <t>NODE_S1984_85_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19623,6 +19643,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -19656,6 +19684,8 @@
           <t>NODE_S1984_85_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19665,6 +19695,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -20054,6 +20092,8 @@
           <t>NODE_S1984_85_0014</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20068,6 +20108,14 @@
         <is>
           <t>NODE_S1983_84_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -20143,6 +20191,8 @@
           <t>NODE_S1984_85_0014</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20152,6 +20202,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -20378,6 +20436,8 @@
           <t>NODE_S1984_85_0020</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20387,6 +20447,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -21006,6 +21074,8 @@
           <t>NODE_S1984_85_0025</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21015,6 +21085,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -21555,6 +21633,8 @@
           <t>NODE_S1984_85_0044</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21564,6 +21644,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -21597,6 +21685,8 @@
           <t>NODE_S1984_85_0044</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21611,6 +21701,14 @@
         <is>
           <t>NODE_S1983_84_0050</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -21884,6 +21982,8 @@
           <t>NODE_S1984_85_0053</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21898,6 +21998,14 @@
         <is>
           <t>NODE_S1983_84_0056</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -21931,6 +22039,8 @@
           <t>NODE_S1984_85_0053</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21945,6 +22055,14 @@
         <is>
           <t>NODE_S1983_84_0057</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -22475,6 +22593,8 @@
           <t>NODE_S1984_85_0065</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22484,6 +22604,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -22517,6 +22645,8 @@
           <t>NODE_S1984_85_0065</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22526,6 +22656,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -22799,6 +22937,8 @@
           <t>NODE_S1984_85_0075</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22808,6 +22948,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -22888,6 +23036,8 @@
           <t>NODE_S1984_85_0075</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22897,6 +23047,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -23340,6 +23498,8 @@
           <t>NODE_S1984_85_0087</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23349,6 +23509,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -23382,6 +23550,8 @@
           <t>NODE_S1984_85_0087</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23391,6 +23561,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -19632,8 +19637,6 @@
           <t>NODE_S1984_85_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19684,8 +19687,6 @@
           <t>NODE_S1984_85_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20092,8 +20093,6 @@
           <t>NODE_S1984_85_0014</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20191,8 +20190,6 @@
           <t>NODE_S1984_85_0014</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20436,8 +20433,6 @@
           <t>NODE_S1984_85_0020</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21074,8 +21069,6 @@
           <t>NODE_S1984_85_0025</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21633,8 +21626,6 @@
           <t>NODE_S1984_85_0044</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21685,8 +21676,6 @@
           <t>NODE_S1984_85_0044</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21982,8 +21971,6 @@
           <t>NODE_S1984_85_0053</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22039,8 +22026,6 @@
           <t>NODE_S1984_85_0053</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22593,8 +22578,6 @@
           <t>NODE_S1984_85_0065</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22645,8 +22628,6 @@
           <t>NODE_S1984_85_0065</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22937,8 +22918,6 @@
           <t>NODE_S1984_85_0075</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23036,8 +23015,6 @@
           <t>NODE_S1984_85_0075</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23498,8 +23475,6 @@
           <t>NODE_S1984_85_0087</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23550,8 +23525,6 @@
           <t>NODE_S1984_85_0087</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -47760,7 +47733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48012,6 +47985,18 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Karlovy Vary: PTS opraveny na 18; původní hodnota 1 byla vnitřně chybná.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -52186,13 +52186,13 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>12</v>
@@ -52206,7 +52206,7 @@
         <v>18</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -44725,6 +44725,7 @@
         </is>
       </c>
     </row>
+    <row r="450"/>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
@@ -45523,6 +45524,7 @@
         </is>
       </c>
     </row>
+    <row r="470"/>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -49816,7 +49816,6 @@
         </is>
       </c>
     </row>
-    <row r="450"/>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
@@ -50615,7 +50614,6 @@
         </is>
       </c>
     </row>
-    <row r="470"/>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
@@ -60842,7 +60840,7 @@
           <t>CLUB_S1984_85_0022</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60862,7 +60860,7 @@
           <t>CLUB_S1984_85_0029</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60882,7 +60880,7 @@
           <t>CLUB_S1984_85_0063</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60902,7 +60900,7 @@
           <t>CLUB_S1984_85_0071</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60922,7 +60920,7 @@
           <t>CLUB_S1984_85_0074</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60942,7 +60940,7 @@
           <t>CLUB_S1984_85_0077</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60962,7 +60960,7 @@
           <t>CLUB_S1984_85_0080</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60982,7 +60980,7 @@
           <t>CLUB_S1984_85_0085</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61002,7 +61000,7 @@
           <t>CLUB_S1984_85_0149</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61022,7 +61020,7 @@
           <t>CLUB_S1984_85_0153</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61042,7 +61040,7 @@
           <t>CLUB_S1984_85_0166</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61062,7 +61060,7 @@
           <t>CLUB_S1984_85_0219</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61082,7 +61080,7 @@
           <t>CLUB_S1984_85_0262</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -61102,7 +61100,7 @@
           <t>CLUB_S1984_85_0264</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61122,7 +61120,7 @@
           <t>CLUB_S1984_85_0267</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -61142,7 +61140,7 @@
           <t>CLUB_S1984_85_0268</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -61162,7 +61160,7 @@
           <t>CLUB_S1984_85_0274</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61182,7 +61180,7 @@
           <t>CLUB_S1984_85_0275</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61202,7 +61200,7 @@
           <t>CLUB_S1984_85_0278</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61222,7 +61220,7 @@
           <t>CLUB_S1984_85_0291</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -61242,7 +61240,7 @@
           <t>CLUB_S1984_85_0294</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61262,7 +61260,7 @@
           <t>CLUB_S1984_85_0309</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -61282,7 +61280,7 @@
           <t>CLUB_S1984_85_0321</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
@@ -61302,7 +61300,7 @@
           <t>CLUB_S1984_85_0372</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
@@ -61322,7 +61320,7 @@
           <t>CLUB_S1984_85_0376</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61342,7 +61340,7 @@
           <t>CLUB_S1984_85_0384</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -61362,7 +61360,7 @@
           <t>CLUB_S1984_85_0385</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61382,7 +61380,7 @@
           <t>CLUB_S1984_85_0395</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61402,7 +61400,7 @@
           <t>CLUB_S1984_85_0397</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
@@ -61422,7 +61420,7 @@
           <t>CLUB_S1984_85_0440</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61442,7 +61440,7 @@
           <t>CLUB_S1984_85_0466</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61462,7 +61460,7 @@
           <t>CLUB_S1984_85_0477</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'TJ Družstevník Rakovec nad Ondavou — odstoupil v průběhu soutěže' [fix_club_notes_in_block_name]</t>
         </is>
@@ -61482,7 +61480,7 @@
           <t>CLUB_S1984_85_0478</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1983_84_0467 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61502,7 +61500,7 @@
           <t>CLUB_S1984_85_0479</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -24771,7 +24771,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24818,7 +24818,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24860,7 +24860,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24902,7 +24902,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30_Praha L40 finálová skupina</t>
+          <t>Praha, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30_Praha L40 skupina o 5.místo</t>
+          <t>Praha, 4. úroveň, skupina o 5.místo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A</t>
+          <t>Středočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B</t>
+          <t>Středočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25480,7 +25480,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina C</t>
+          <t>Středočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina D</t>
+          <t>Středočeský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finálová skupina</t>
+          <t>Středočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina E</t>
+          <t>Středočeský, 4. úroveň, skupina E</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25658,7 +25658,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina G</t>
+          <t>Středočeský, 4. úroveň, skupina G</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Středočeský Kvalifikace o KP</t>
+          <t>Středočeský Kvalifikace o KP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A (Kutná Hora ,Kolín)</t>
+          <t>Středočeský, 4. úroveň, skupina A (Kutná Hora ,Kolín)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B (Beroun ,Příbram ,Praha Západ)</t>
+          <t>Středočeský, 4. úroveň, skupina B (Beroun ,Příbram ,Praha Západ)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina C (Kladno ,….)</t>
+          <t>Středočeský, 4. úroveň, skupina C (Kladno ,….)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finále</t>
+          <t>Středočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina D (Mladá Boleslav ,Praha Východ)</t>
+          <t>Středočeský, 4. úroveň, skupina D (Mladá Boleslav ,Praha Východ)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -26064,7 +26064,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Jihočeský O postup do KP</t>
+          <t>Jihočeský O postup do KP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Jihočeský Kvalifikace o KP</t>
+          <t>Jihočeský Kvalifikace o KP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -26205,7 +26205,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina A</t>
+          <t>Západočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina B</t>
+          <t>Západočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina C</t>
+          <t>Západočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 finálová skupina</t>
+          <t>Západočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -26435,7 +26435,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 o umístění</t>
+          <t>Západočeský, 4. úroveň o umístění</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 finále</t>
+          <t>Západočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -26540,7 +26540,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Západočeský kvalifikace o I.třídu</t>
+          <t>Západočeský kvalifikace o I.třídu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -26639,7 +26639,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 skupina A</t>
+          <t>Severočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -26733,7 +26733,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 skupina B</t>
+          <t>Severočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 finále</t>
+          <t>Severočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 o udržení</t>
+          <t>Severočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina A</t>
+          <t>Východočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina B</t>
+          <t>Východočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -27068,7 +27068,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finálová skupina</t>
+          <t>Východočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský kvalifikace o KS</t>
+          <t>Východočeský kvalifikace o KS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -27157,7 +27157,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -27298,7 +27298,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -27345,7 +27345,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -27387,7 +27387,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o umístění skupina A</t>
+          <t>Jihomoravský, 4. úroveň o umístění skupina A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -27437,7 +27437,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o umístění skupina B</t>
+          <t>Jihomoravský, 4. úroveň o umístění skupina B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský Kvalifikace o KP</t>
+          <t>Jihomoravský Kvalifikace o KP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -27586,7 +27586,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní skupina</t>
+          <t>Severomoravský, 4. úroveň, základní skupina</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -27777,7 +27777,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finálová skupina</t>
+          <t>Severomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina o 5.-8.místo</t>
+          <t>Severomoravský, 4. úroveň, skupina o 5.-8.místo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 KP II.třídy</t>
+          <t>Severomoravský, 4. úroveň KP II.třídy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -27916,7 +27916,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Severomoravský Kvalifikace o postup do KS</t>
+          <t>Severomoravský Kvalifikace o postup do KS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -27963,7 +27963,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_SVK Západoslovenský krajský přebor</t>
+          <t>Slovensko Západoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_SVK Západoslovenský kraj</t>
+          <t>Slovensko Západoslovenský kraj</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -28042,7 +28042,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_SVK Středoslovenský kraj</t>
+          <t>Slovensko Středoslovenský kraj</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_SVK Východoslovenský kraj</t>
+          <t>Slovensko Východoslovenský kraj</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_SVK Středoslovenský krajský přebor</t>
+          <t>Slovensko Středoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -28158,7 +28158,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_SVK Východoslovenský krajský přebor</t>
+          <t>Slovensko Východoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_SVK Východoslovenský krajský přebor – východní skupina</t>
+          <t>Slovensko Východoslovenský krajský přebor – východní skupina</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_SVK Východoslovenský krajský přebor – západní skupina</t>
+          <t>Slovensko Východoslovenský krajský přebor – západní skupina</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_SVK Východoslovenský krajský přebor – finále</t>
+          <t>Slovensko Východoslovenský krajský přebor – finále</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_SVK Východoslovenský krajský přebor – O 5.-11.místo</t>
+          <t>Slovensko Východoslovenský krajský přebor – O 5.-11.místo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">

--- a/data/S1984_85_FINAL.xlsx
+++ b/data/S1984_85_FINAL.xlsx
@@ -61810,7 +61810,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -65578,7 +65578,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -65656,7 +65656,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -65734,7 +65734,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -65812,7 +65812,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -65890,7 +65890,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -65963,7 +65963,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -66036,7 +66036,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -66114,7 +66114,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
